--- a/showcase/fitness-crm/results/gym-crm-test-suite.xlsx
+++ b/showcase/fitness-crm/results/gym-crm-test-suite.xlsx
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4184" uniqueCount="1768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4185" uniqueCount="1767">
   <si>
     <t xml:space="preserve">Gym CRM full regression</t>
   </si>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">AI: keyless stand-in (drafts and readiness from a heuristic, not a model)</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated 2026-10-16 from the agent run against http://localhost:3410 (Gym CRM (fitness-crm sample, demo data)).</t>
+    <t xml:space="preserve">Generated 2026-10-23 from the agent run against http://localhost:3410 (Gym CRM (fitness-crm sample, demo data)).</t>
   </si>
   <si>
     <t xml:space="preserve">Yellow cells on the module sheets are for testers: Tester result (Pass, Fail, Blocked, Not run), notes and date.</t>
@@ -2208,10 +2208,11 @@
     <t xml:space="preserve">BR-301</t>
   </si>
   <si>
-    <t xml:space="preserve">A contract's end date is computed from the tier: PT 24 sessions ends 181 days after the start.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 24 sessions starting today → End date = today + 181 days</t>
+    <t xml:space="preserve">A contract's end date is computed from the tier: PT 24 sessions has 181 days of validity counting the start day (A-108), so the contract ends 180 days after its start; with no start date typed, the start is today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. New PT contract, 24 sessions, no start date typed → Ngày kết thúc = today + 180 days
+2. Type a start date of today + 10 → Ngày kết thúc = today + 190 days</t>
   </si>
   <si>
     <t xml:space="preserve">CON-09</t>
@@ -3857,9 +3858,6 @@
     <t xml:space="preserve">1. Open /contracts/00000000-0000-4000-8000-000000000000 → "Không tìm thấy"</t>
   </si>
   <si>
-    <t xml:space="preserve">INCONCLUSIVE</t>
-  </si>
-  <si>
     <t xml:space="preserve">SEC-02</t>
   </si>
   <si>
@@ -4097,7 +4095,7 @@
     <t xml:space="preserve">CUS-01: PASSED, CUS-02: PASSED, CUS-03: PASSED, CUS-04: PASSED, CUS-05: PASSED, CUS-06: manual</t>
   </si>
   <si>
-    <t xml:space="preserve">CON-08: manual</t>
+    <t xml:space="preserve">CON-08: PASSED</t>
   </si>
   <si>
     <t xml:space="preserve">CON-09: manual</t>
@@ -4217,7 +4215,7 @@
     <t xml:space="preserve">CON-16, SEC-01</t>
   </si>
   <si>
-    <t xml:space="preserve">CON-16: PASSED, SEC-01: INCONCLUSIVE</t>
+    <t xml:space="preserve">CON-16: PASSED, SEC-01: PASSED</t>
   </si>
   <si>
     <t xml:space="preserve">CUS-11, CUS-12</t>
@@ -5598,7 +5596,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5614,24 +5612,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE3F3E8"/>
-        <bgColor rgb="FFFDF0D9"/>
+        <bgColor rgb="FFFBE7E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFDF0D9"/>
+        <bgColor rgb="FFFBE7E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBE7E5"/>
-        <bgColor rgb="FFFDF0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF0D9"/>
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
@@ -5685,7 +5677,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5734,10 +5726,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5751,7 +5739,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -5799,14 +5787,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFDF0D9"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -5845,11 +5825,11 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFDF0D9"/>
+      <rgbColor rgb="FFFBE7E5"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFBE7E5"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -6257,11 +6237,11 @@
       </c>
       <c r="D9" s="4" t="n">
         <f aca="false">COUNTIF('Customers &amp; contracts'!J:J,"Automated")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" s="4" t="n">
         <f aca="false">COUNTIF('Customers &amp; contracts'!J:J,"Manual")</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" s="4" t="n">
         <f aca="false">COUNTIF('Customers &amp; contracts'!J:J,"Not drafted")</f>
@@ -6269,7 +6249,7 @@
       </c>
       <c r="G9" s="4" t="n">
         <f aca="false">COUNTIF('Customers &amp; contracts'!M:M,"PASSED")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" s="4" t="n">
         <f aca="false">COUNTIF('Customers &amp; contracts'!M:M,"FAILED")</f>
@@ -6365,7 +6345,7 @@
       </c>
       <c r="G11" s="4" t="n">
         <f aca="false">COUNTIF(Operations!M:M,"PASSED")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="4" t="n">
         <f aca="false">COUNTIF(Operations!M:M,"FAILED")</f>
@@ -6373,7 +6353,7 @@
       </c>
       <c r="I11" s="4" t="n">
         <f aca="false">COUNTIF(Operations!M:M,"INCONCLUSIVE")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
         <f aca="false">COUNTIF(Operations!O:O,"Pass")</f>
@@ -6399,11 +6379,11 @@
       </c>
       <c r="D12" s="5" t="n">
         <f aca="false">SUM(D7:D11)</f>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E12" s="5" t="n">
         <f aca="false">SUM(E7:E11)</f>
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F12" s="5" t="n">
         <f aca="false">SUM(F7:F11)</f>
@@ -6411,7 +6391,7 @@
       </c>
       <c r="G12" s="5" t="n">
         <f aca="false">SUM(G7:G11)</f>
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H12" s="5" t="n">
         <f aca="false">SUM(H7:H11)</f>
@@ -6419,7 +6399,7 @@
       </c>
       <c r="I12" s="5" t="n">
         <f aca="false">SUM(I7:I11)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
         <f aca="false">SUM(J7:J11)</f>
@@ -6440,7 +6420,7 @@
       </c>
       <c r="C13" s="7" t="n">
         <f aca="false">IF(C12=0,0,D12/C12)</f>
-        <v>0.498084291187739</v>
+        <v>0.501915708812261</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12867,7 +12847,7 @@
       <c r="P24" s="10"/>
       <c r="Q24" s="10"/>
     </row>
-    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
         <v>676</v>
       </c>
@@ -12894,13 +12874,15 @@
         <v>680</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>60</v>
+      </c>
       <c r="N25" s="8"/>
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
@@ -17472,11 +17454,11 @@
         <v>7</v>
       </c>
       <c r="K55" s="8"/>
-      <c r="L55" s="12" t="s">
-        <v>1214</v>
-      </c>
-      <c r="M55" s="12" t="s">
-        <v>1214</v>
+      <c r="L55" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="N55" s="8"/>
       <c r="O55" s="10"/>
@@ -17485,7 +17467,7 @@
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>1210</v>
@@ -17497,17 +17479,17 @@
         <v>54</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>72</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>7</v>
@@ -17526,7 +17508,7 @@
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>1210</v>
@@ -17538,17 +17520,17 @@
         <v>54</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>72</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H57" s="8"/>
       <c r="I57" s="8" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="J57" s="8" t="s">
         <v>7</v>
@@ -17567,7 +17549,7 @@
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>1210</v>
@@ -17579,17 +17561,17 @@
         <v>54</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>72</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="J58" s="8" t="s">
         <v>7</v>
@@ -17608,7 +17590,7 @@
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>1210</v>
@@ -17620,17 +17602,17 @@
         <v>54</v>
       </c>
       <c r="E59" s="8" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F59" s="8" t="s">
         <v>1228</v>
       </c>
-      <c r="F59" s="8" t="s">
+      <c r="G59" s="8" t="s">
         <v>1229</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>1230</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="J59" s="8" t="s">
         <v>9</v>
@@ -17684,27 +17666,27 @@
         <v>40</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>1229</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>1230</v>
-      </c>
       <c r="C2" s="8" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="270.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17715,10 +17697,10 @@
         <v>73</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>1235</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17729,10 +17711,10 @@
         <v>1080</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>1237</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17746,7 +17728,7 @@
         <v>1066</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17757,10 +17739,10 @@
         <v>433</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>1240</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17771,10 +17753,10 @@
         <v>1027</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>1242</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17788,7 +17770,7 @@
         <v>547</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17802,7 +17784,7 @@
         <v>1185</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17813,10 +17795,10 @@
         <v>647</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>1246</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17830,7 +17812,7 @@
         <v>743</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17844,7 +17826,7 @@
         <v>1051</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17858,7 +17840,7 @@
         <v>748</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17872,7 +17854,7 @@
         <v>917</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17886,7 +17868,7 @@
         <v>897</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17900,7 +17882,7 @@
         <v>1135</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17911,10 +17893,10 @@
         <v>1009</v>
       </c>
       <c r="C17" s="8" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>1254</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17925,10 +17907,10 @@
         <v>990</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>1256</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17942,7 +17924,7 @@
         <v>1155</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17953,10 +17935,10 @@
         <v>1169</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>1259</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17970,7 +17952,7 @@
         <v>1204</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17984,7 +17966,7 @@
         <v>1180</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17998,7 +17980,7 @@
         <v>850</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18009,10 +17991,10 @@
         <v>375</v>
       </c>
       <c r="C24" s="8" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>1264</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18023,10 +18005,10 @@
         <v>512</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>1266</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18037,10 +18019,10 @@
         <v>541</v>
       </c>
       <c r="C26" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>1268</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18051,10 +18033,10 @@
         <v>1041</v>
       </c>
       <c r="C27" s="8" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>1270</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18065,10 +18047,10 @@
         <v>943</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>1272</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18082,7 +18064,7 @@
         <v>950</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18093,10 +18075,10 @@
         <v>352</v>
       </c>
       <c r="C30" s="8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>1275</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18110,7 +18092,7 @@
         <v>1072</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18121,10 +18103,10 @@
         <v>632</v>
       </c>
       <c r="C32" s="8" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>1278</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18138,7 +18120,7 @@
         <v>1001</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18152,7 +18134,7 @@
         <v>1056</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18166,7 +18148,7 @@
         <v>1061</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18177,10 +18159,10 @@
         <v>57</v>
       </c>
       <c r="C36" s="8" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>1283</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18191,10 +18173,10 @@
         <v>404</v>
       </c>
       <c r="C37" s="8" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>1285</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18205,10 +18187,10 @@
         <v>507</v>
       </c>
       <c r="C38" s="8" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>1287</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18219,10 +18201,10 @@
         <v>522</v>
       </c>
       <c r="C39" s="8" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>1289</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18236,7 +18218,7 @@
         <v>533</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18247,13 +18229,13 @@
         <v>570</v>
       </c>
       <c r="C41" s="8" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>1292</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
         <v>678</v>
       </c>
@@ -18264,7 +18246,7 @@
         <v>676</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18278,7 +18260,7 @@
         <v>681</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18292,7 +18274,7 @@
         <v>686</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18303,10 +18285,10 @@
         <v>711</v>
       </c>
       <c r="C45" s="8" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D45" s="8" t="s">
         <v>1297</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18320,7 +18302,7 @@
         <v>697</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18334,7 +18316,7 @@
         <v>753</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18348,7 +18330,7 @@
         <v>692</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18362,7 +18344,7 @@
         <v>777</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18376,7 +18358,7 @@
         <v>867</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18387,10 +18369,10 @@
         <v>706</v>
       </c>
       <c r="C51" s="8" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>1304</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18401,10 +18383,10 @@
         <v>829</v>
       </c>
       <c r="C52" s="8" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D52" s="8" t="s">
         <v>1306</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>1307</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18415,10 +18397,10 @@
         <v>877</v>
       </c>
       <c r="C53" s="8" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D53" s="8" t="s">
         <v>1308</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18432,7 +18414,7 @@
         <v>887</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18446,7 +18428,7 @@
         <v>902</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18460,7 +18442,7 @@
         <v>907</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18474,7 +18456,7 @@
         <v>892</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18485,10 +18467,10 @@
         <v>926</v>
       </c>
       <c r="C58" s="8" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>1314</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18502,7 +18484,7 @@
         <v>1161</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18516,7 +18498,7 @@
         <v>1171</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18530,7 +18512,7 @@
         <v>978</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18541,10 +18523,10 @@
         <v>716</v>
       </c>
       <c r="C62" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D62" s="8" t="s">
         <v>1319</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18555,10 +18537,10 @@
         <v>959</v>
       </c>
       <c r="C63" s="8" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D63" s="8" t="s">
         <v>1321</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18569,10 +18551,10 @@
         <v>968</v>
       </c>
       <c r="C64" s="8" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D64" s="8" t="s">
         <v>1323</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18586,7 +18568,7 @@
         <v>996</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18600,7 +18582,7 @@
         <v>1140</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18614,7 +18596,7 @@
         <v>1121</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18628,7 +18610,7 @@
         <v>634</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18642,7 +18624,7 @@
         <v>763</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18653,10 +18635,10 @@
         <v>761</v>
       </c>
       <c r="C70" s="8" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D70" s="8" t="s">
         <v>1330</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18670,7 +18652,7 @@
         <v>772</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18681,10 +18663,10 @@
         <v>721</v>
       </c>
       <c r="C72" s="8" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D72" s="8" t="s">
         <v>1333</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18695,10 +18677,10 @@
         <v>618</v>
       </c>
       <c r="C73" s="8" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D73" s="8" t="s">
         <v>1335</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18709,10 +18691,10 @@
         <v>600</v>
       </c>
       <c r="C74" s="8" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D74" s="8" t="s">
         <v>1337</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18726,7 +18708,7 @@
         <v>610</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18740,7 +18722,7 @@
         <v>624</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18754,7 +18736,7 @@
         <v>494</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18765,10 +18747,10 @@
         <v>487</v>
       </c>
       <c r="C78" s="8" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D78" s="8" t="s">
         <v>1342</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18782,7 +18764,7 @@
         <v>552</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18793,10 +18775,10 @@
         <v>470</v>
       </c>
       <c r="C80" s="8" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D80" s="8" t="s">
         <v>1345</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18810,7 +18792,7 @@
         <v>462</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18824,7 +18806,7 @@
         <v>561</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18838,7 +18820,7 @@
         <v>1145</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18852,7 +18834,7 @@
         <v>1082</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18866,7 +18848,7 @@
         <v>361</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18877,10 +18859,10 @@
         <v>1036</v>
       </c>
       <c r="C86" s="8" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D86" s="8" t="s">
         <v>1352</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18894,7 +18876,7 @@
         <v>1150</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18905,10 +18887,10 @@
         <v>848</v>
       </c>
       <c r="C88" s="8" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D88" s="8" t="s">
         <v>1355</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18922,7 +18904,7 @@
         <v>840</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18936,7 +18918,7 @@
         <v>912</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18947,10 +18929,10 @@
         <v>1198</v>
       </c>
       <c r="C91" s="8" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D91" s="8" t="s">
         <v>1359</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18964,7 +18946,7 @@
         <v>1092</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18975,10 +18957,10 @@
         <v>1090</v>
       </c>
       <c r="C93" s="8" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D93" s="8" t="s">
         <v>1362</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>1363</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18992,7 +18974,7 @@
         <v>1097</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19006,7 +18988,7 @@
         <v>1110</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19020,7 +19002,7 @@
         <v>1116</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19034,7 +19016,7 @@
         <v>1130</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
   </sheetData>
@@ -19069,12 +19051,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
         <v>1368</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>1369</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>31</v>
@@ -19082,13 +19064,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>1370</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>1371</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1372</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
@@ -19096,13 +19078,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>1373</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>1374</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>1375</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>52</v>
@@ -19110,13 +19092,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>1376</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>1377</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>1378</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>61</v>
@@ -19124,13 +19106,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>1379</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>1380</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>1381</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>65</v>
@@ -19138,13 +19120,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>1382</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>1383</v>
-      </c>
       <c r="C8" s="8" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>92</v>
@@ -19152,21 +19134,21 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>1384</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>1385</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>1386</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>1387</v>
+      <c r="A11" s="12" t="s">
+        <v>1386</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>34</v>
@@ -19174,13 +19156,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>1388</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>1389</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>1390</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>6</v>
@@ -19188,27 +19170,27 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>1391</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>1392</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="8" t="s">
         <v>1393</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>1395</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>1396</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>52</v>
@@ -19219,10 +19201,10 @@
         <v>112</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>81</v>
@@ -19233,18 +19215,18 @@
         <v>112</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>1399</v>
+      <c r="A18" s="12" t="s">
+        <v>1398</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
@@ -19252,21 +19234,21 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>1400</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>1372</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>1402</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>1403</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>103</v>
@@ -19274,18 +19256,18 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>1404</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>1405</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>1406</v>
+      <c r="A23" s="12" t="s">
+        <v>1405</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>33</v>
@@ -19293,16 +19275,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>1407</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>1408</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>1409</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>1410</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>6</v>
@@ -19310,517 +19292,517 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>1411</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>1412</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>1413</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="E25" s="8" t="s">
         <v>1414</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>1415</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>1416</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="C26" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>1417</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>1419</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="C27" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>1420</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>1421</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>1422</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>1424</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="C29" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>1425</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>1427</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="C30" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>1428</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>1430</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="C31" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>1431</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>1433</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="C32" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E32" s="8" t="s">
         <v>1434</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>1435</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>1436</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="C33" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E33" s="8" t="s">
         <v>1437</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>1439</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="C34" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E34" s="8" t="s">
         <v>1440</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>1442</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D35" s="8" t="s">
+      <c r="E35" s="8" t="s">
         <v>1443</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B36" s="8" t="s">
         <v>1445</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="C36" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>1446</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="D36" s="8" t="s">
+      <c r="E36" s="8" t="s">
         <v>1447</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>1449</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="C37" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E37" s="8" t="s">
         <v>1450</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>1447</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>1451</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>1452</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="C38" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E38" s="8" t="s">
         <v>1453</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>1455</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="C39" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>1456</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D39" s="8" t="s">
+      <c r="E39" s="8" t="s">
         <v>1457</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B40" s="8" t="s">
         <v>1459</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="C40" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>1460</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>1461</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>1462</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="C41" s="8" t="s">
         <v>1463</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="D41" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>1464</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B42" s="8" t="s">
         <v>1466</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="C42" s="8" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>1467</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>1464</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>1469</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="C43" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E43" s="8" t="s">
         <v>1470</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>1457</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B44" s="8" t="s">
         <v>1472</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="C44" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E44" s="8" t="s">
         <v>1473</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>1474</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>1475</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="C45" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>1476</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>1447</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>1477</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B46" s="8" t="s">
         <v>1478</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="C46" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E46" s="8" t="s">
         <v>1479</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>1457</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>1481</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="C47" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E47" s="8" t="s">
         <v>1482</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>1457</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>1483</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>1484</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="C48" s="8" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>1485</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>1464</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>1487</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="C49" s="8" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>1488</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>1464</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>1489</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>1490</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="C50" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E50" s="8" t="s">
         <v>1491</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>1457</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>1447</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>1492</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>1493</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="C51" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>1494</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>1496</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>1457</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>1497</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B53" s="8" t="s">
         <v>1498</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="C53" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E53" s="8" t="s">
         <v>1499</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>1457</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>1500</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B54" s="8" t="s">
         <v>1501</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="C54" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E54" s="8" t="s">
         <v>1502</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>1443</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>1457</v>
-      </c>
-      <c r="E54" s="8" t="s">
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="12" t="s">
         <v>1503</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="13" t="s">
-        <v>1504</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>31</v>
@@ -19828,41 +19810,41 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>1370</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>1371</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>1372</v>
-      </c>
       <c r="D57" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>1505</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="C58" s="8" t="s">
         <v>1506</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="D58" s="8" t="s">
         <v>1507</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>1509</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="C59" s="8" t="s">
         <v>1510</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>1511</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>377</v>
@@ -19870,13 +19852,13 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>1512</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>1513</v>
-      </c>
       <c r="C60" s="8" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>381</v>
@@ -19884,13 +19866,13 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>1514</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="C61" s="8" t="s">
         <v>1515</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>1516</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>393</v>
@@ -19898,13 +19880,13 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>1517</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="C62" s="8" t="s">
         <v>1518</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>1519</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>484</v>
@@ -19912,21 +19894,21 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B63" s="8" t="s">
         <v>1520</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="C63" s="8" t="s">
         <v>1521</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>1522</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="13" t="s">
-        <v>1523</v>
+      <c r="A65" s="12" t="s">
+        <v>1522</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>29</v>
@@ -19934,27 +19916,27 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>1524</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>1525</v>
-      </c>
       <c r="C66" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B67" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>1527</v>
-      </c>
       <c r="C67" s="8" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>377</v>
@@ -19962,13 +19944,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B68" s="8" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>1528</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>1529</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>385</v>
@@ -19976,13 +19958,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>389</v>
@@ -19990,13 +19972,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>393</v>
@@ -20004,13 +19986,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>1532</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="C71" s="8" t="s">
         <v>1533</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>1534</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>401</v>
@@ -20018,13 +20000,13 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>406</v>
@@ -20032,13 +20014,13 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>410</v>
@@ -20046,21 +20028,21 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="13" t="s">
-        <v>1538</v>
+      <c r="A76" s="12" t="s">
+        <v>1537</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>31</v>
@@ -20068,27 +20050,27 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>1370</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>1371</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>1372</v>
-      </c>
       <c r="D77" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>372</v>
@@ -20096,13 +20078,13 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B79" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>1541</v>
-      </c>
       <c r="C79" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>406</v>
@@ -20110,13 +20092,13 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>1542</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="C80" s="8" t="s">
         <v>1543</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>1544</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>422</v>
@@ -20124,13 +20106,13 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B81" s="8" t="s">
         <v>1545</v>
       </c>
-      <c r="B81" s="8" t="s">
-        <v>1546</v>
-      </c>
       <c r="C81" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>426</v>
@@ -20138,13 +20120,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B82" s="8" t="s">
         <v>1547</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="C82" s="8" t="s">
         <v>1548</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>1549</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>418</v>
@@ -20152,13 +20134,13 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B83" s="8" t="s">
         <v>1550</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="C83" s="8" t="s">
         <v>1551</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>1552</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>443</v>
@@ -20166,21 +20148,21 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B84" s="8" t="s">
         <v>1553</v>
       </c>
-      <c r="B84" s="8" t="s">
-        <v>1554</v>
-      </c>
       <c r="C84" s="8" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="13" t="s">
-        <v>1555</v>
+      <c r="A86" s="12" t="s">
+        <v>1554</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>30</v>
@@ -20188,27 +20170,27 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>1556</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>1557</v>
-      </c>
       <c r="C87" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B88" s="8" t="s">
         <v>1558</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="C88" s="8" t="s">
         <v>1559</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>1560</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>430</v>
@@ -20216,13 +20198,13 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>435</v>
@@ -20230,13 +20212,13 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>439</v>
@@ -20244,21 +20226,21 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B91" s="8" t="s">
         <v>1562</v>
       </c>
-      <c r="B91" s="8" t="s">
-        <v>1563</v>
-      </c>
       <c r="C91" s="8" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="13" t="s">
-        <v>1564</v>
+      <c r="A93" s="12" t="s">
+        <v>1563</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>30</v>
@@ -20266,109 +20248,109 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>1565</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>1566</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="D94" s="3" t="s">
         <v>1567</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>1568</v>
-      </c>
       <c r="E94" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E95" s="8" t="s">
         <v>1569</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>1569</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>1569</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>1569</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>1570</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="E99" s="8" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="12" t="s">
         <v>1571</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="13" t="s">
-        <v>1572</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>34</v>
@@ -20376,13 +20358,13 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>1388</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="C102" s="3" t="s">
         <v>1389</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>1390</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>6</v>
@@ -20390,13 +20372,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B103" s="8" t="s">
         <v>1573</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="C103" s="8" t="s">
         <v>1574</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>1575</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>519</v>
@@ -20404,13 +20386,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="8" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B104" s="8" t="s">
         <v>1575</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="C104" s="8" t="s">
         <v>1576</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>1577</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>519</v>
@@ -20418,13 +20400,13 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B105" s="8" t="s">
         <v>1577</v>
       </c>
-      <c r="B105" s="8" t="s">
+      <c r="C105" s="8" t="s">
         <v>1578</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>1579</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>533</v>
@@ -20432,13 +20414,13 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="8" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B106" s="8" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C106" s="8" t="s">
         <v>1580</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>1581</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>529</v>
@@ -20446,13 +20428,13 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B107" s="8" t="s">
         <v>1582</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="C107" s="8" t="s">
         <v>1583</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>1584</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>524</v>
@@ -20460,21 +20442,21 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B108" s="8" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C108" s="8" t="s">
         <v>1585</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>1586</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="13" t="s">
-        <v>1587</v>
+      <c r="A110" s="12" t="s">
+        <v>1586</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>31</v>
@@ -20482,27 +20464,27 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>1588</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>1589</v>
-      </c>
       <c r="D111" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="8" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B112" s="8" t="s">
         <v>1590</v>
       </c>
-      <c r="B112" s="8" t="s">
+      <c r="C112" s="8" t="s">
         <v>1591</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>1592</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>566</v>
@@ -20510,13 +20492,13 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="8" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B113" s="8" t="s">
         <v>1593</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="C113" s="8" t="s">
         <v>1594</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>1595</v>
       </c>
       <c r="D113" s="8" t="s">
         <v>573</v>
@@ -20524,13 +20506,13 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="8" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B114" s="8" t="s">
         <v>1596</v>
       </c>
-      <c r="B114" s="8" t="s">
+      <c r="C114" s="8" t="s">
         <v>1597</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>1598</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>578</v>
@@ -20538,13 +20520,13 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B115" s="8" t="s">
         <v>1599</v>
       </c>
-      <c r="B115" s="8" t="s">
+      <c r="C115" s="8" t="s">
         <v>1600</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>1601</v>
       </c>
       <c r="D115" s="8" t="s">
         <v>583</v>
@@ -20552,21 +20534,21 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="8" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B116" s="8" t="s">
         <v>1602</v>
       </c>
-      <c r="B116" s="8" t="s">
+      <c r="C116" s="8" t="s">
         <v>1603</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>1604</v>
       </c>
       <c r="D116" s="8" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="13" t="s">
-        <v>1605</v>
+      <c r="A118" s="12" t="s">
+        <v>1604</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>29</v>
@@ -20574,21 +20556,21 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="8" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B120" s="8" t="s">
         <v>1606</v>
-      </c>
-      <c r="B120" s="8" t="s">
-        <v>1607</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>658</v>
@@ -20596,10 +20578,10 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="8" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B121" s="8" t="s">
         <v>1608</v>
-      </c>
-      <c r="B121" s="8" t="s">
-        <v>1609</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>643</v>
@@ -20607,10 +20589,10 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="8" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B122" s="8" t="s">
         <v>1610</v>
-      </c>
-      <c r="B122" s="8" t="s">
-        <v>1611</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>650</v>
@@ -20618,10 +20600,10 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="8" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B123" s="8" t="s">
         <v>1612</v>
-      </c>
-      <c r="B123" s="8" t="s">
-        <v>1613</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>654</v>
@@ -20629,29 +20611,29 @@
     </row>
     <row r="124" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="8" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B124" s="8" t="s">
         <v>1614</v>
       </c>
-      <c r="B124" s="8" t="s">
+      <c r="C124" s="8" t="s">
         <v>1615</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>1616</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="8" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B125" s="8" t="s">
         <v>1617</v>
-      </c>
-      <c r="B125" s="8" t="s">
-        <v>1618</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>666</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="13" t="s">
-        <v>1619</v>
+      <c r="A127" s="12" t="s">
+        <v>1618</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>29</v>
@@ -20659,21 +20641,21 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="8" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>593</v>
@@ -20681,29 +20663,29 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="8" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C130" s="8" t="s">
         <v>1622</v>
-      </c>
-      <c r="B130" s="8" t="s">
-        <v>1595</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>1623</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="8" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="13" t="s">
-        <v>1625</v>
+      <c r="A133" s="12" t="s">
+        <v>1624</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>34</v>
@@ -20711,13 +20693,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B134" s="3" t="s">
         <v>1388</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="C134" s="3" t="s">
         <v>1389</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>1390</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>6</v>
@@ -20725,13 +20707,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B135" s="8" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C135" s="8" t="s">
         <v>1626</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>1627</v>
       </c>
       <c r="D135" s="8" t="s">
         <v>731</v>
@@ -20739,27 +20721,27 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="8" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B136" s="8" t="s">
         <v>1628</v>
       </c>
-      <c r="B136" s="8" t="s">
+      <c r="C136" s="8" t="s">
         <v>1629</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="D136" s="8" t="s">
         <v>1630</v>
-      </c>
-      <c r="D136" s="8" t="s">
-        <v>1631</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="8" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B137" s="8" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C137" s="8" t="s">
         <v>1632</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>1633</v>
       </c>
       <c r="D137" s="8" t="s">
         <v>735</v>
@@ -20767,13 +20749,13 @@
     </row>
     <row r="138" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="8" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B138" s="8" t="s">
         <v>1634</v>
       </c>
-      <c r="B138" s="8" t="s">
-        <v>1635</v>
-      </c>
       <c r="C138" s="8" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="D138" s="8" t="s">
         <v>739</v>
@@ -20781,13 +20763,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="8" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B139" s="8" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C139" s="8" t="s">
         <v>1636</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>1637</v>
       </c>
       <c r="D139" s="8" t="s">
         <v>748</v>
@@ -20795,13 +20777,13 @@
     </row>
     <row r="140" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="8" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B140" s="8" t="s">
         <v>1637</v>
       </c>
-      <c r="B140" s="8" t="s">
+      <c r="C140" s="8" t="s">
         <v>1638</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>1639</v>
       </c>
       <c r="D140" s="8" t="s">
         <v>748</v>
@@ -20809,13 +20791,13 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="8" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="D141" s="8" t="s">
         <v>703</v>
@@ -20823,21 +20805,21 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="8" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B142" s="8" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C142" s="8" t="s">
         <v>1641</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="D142" s="8" t="s">
         <v>1642</v>
       </c>
-      <c r="D142" s="8" t="s">
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="12" t="s">
         <v>1643</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="13" t="s">
-        <v>1644</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>30</v>
@@ -20845,77 +20827,77 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B145" s="3" t="s">
         <v>1645</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="C145" s="3" t="s">
         <v>1646</v>
       </c>
-      <c r="C145" s="3" t="s">
-        <v>1647</v>
-      </c>
       <c r="D145" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="8" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D149" s="8" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="12" t="s">
         <v>1650</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="13" t="s">
-        <v>1651</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>30</v>
@@ -20923,57 +20905,57 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B152" s="3" t="s">
         <v>1652</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="C152" s="3" t="s">
         <v>1653</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="D152" s="3" t="s">
         <v>1654</v>
       </c>
-      <c r="D152" s="3" t="s">
+      <c r="E152" s="3" t="s">
         <v>1655</v>
       </c>
-      <c r="E152" s="3" t="s">
+      <c r="F152" s="3" t="s">
         <v>1656</v>
       </c>
-      <c r="F152" s="3" t="s">
+      <c r="G152" s="3" t="s">
         <v>1657</v>
       </c>
-      <c r="G152" s="3" t="s">
-        <v>1658</v>
-      </c>
       <c r="H152" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="8" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>1658</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>1658</v>
+      </c>
+      <c r="H153" s="8" t="s">
         <v>1659</v>
-      </c>
-      <c r="B153" s="8" t="s">
-        <v>1659</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D153" s="8" t="s">
-        <v>1659</v>
-      </c>
-      <c r="E153" s="8" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F153" s="8" t="s">
-        <v>1659</v>
-      </c>
-      <c r="G153" s="8" t="s">
-        <v>1659</v>
-      </c>
-      <c r="H153" s="8" t="s">
-        <v>1660</v>
       </c>
       <c r="I153" s="8" t="s">
         <v>782</v>
@@ -20981,28 +20963,28 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="8" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="H154" s="8" t="s">
         <v>1661</v>
-      </c>
-      <c r="B154" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D154" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="E154" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F154" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="H154" s="8" t="s">
-        <v>1662</v>
       </c>
       <c r="I154" s="8" t="s">
         <v>788</v>
@@ -21010,28 +20992,28 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="8" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D155" s="8" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="H155" s="8" t="s">
         <v>1661</v>
-      </c>
-      <c r="E155" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F155" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="G155" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="H155" s="8" t="s">
-        <v>1662</v>
       </c>
       <c r="I155" s="8" t="s">
         <v>793</v>
@@ -21039,28 +21021,28 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="8" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H156" s="8" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="I156" s="8" t="s">
         <v>797</v>
@@ -21068,28 +21050,28 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="B157" s="8" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="H157" s="8" t="s">
         <v>1665</v>
-      </c>
-      <c r="C157" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D157" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="E157" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F157" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="G157" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="H157" s="8" t="s">
-        <v>1666</v>
       </c>
       <c r="I157" s="8" t="s">
         <v>801</v>
@@ -21097,28 +21079,28 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H158" s="8" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="I158" s="8" t="s">
         <v>806</v>
@@ -21126,28 +21108,28 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="I159" s="8" t="s">
         <v>811</v>
@@ -21155,28 +21137,28 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="I160" s="8" t="s">
         <v>816</v>
@@ -21184,28 +21166,28 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="I161" s="8" t="s">
         <v>826</v>
@@ -21213,36 +21195,36 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="I162" s="8" t="s">
         <v>832</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="13" t="s">
-        <v>1672</v>
+      <c r="A164" s="12" t="s">
+        <v>1671</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>30</v>
@@ -21250,27 +21232,27 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B165" s="3" t="s">
         <v>1673</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="C165" s="3" t="s">
         <v>1674</v>
       </c>
-      <c r="C165" s="3" t="s">
-        <v>1675</v>
-      </c>
       <c r="D165" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="8" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D166" s="8" t="s">
         <v>874</v>
@@ -21278,13 +21260,13 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="8" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D167" s="8" t="s">
         <v>879</v>
@@ -21292,13 +21274,13 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="8" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D168" s="8" t="s">
         <v>883</v>
@@ -21306,13 +21288,13 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="8" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B169" s="8" t="s">
         <v>1679</v>
       </c>
-      <c r="B169" s="8" t="s">
+      <c r="C169" s="8" t="s">
         <v>1680</v>
-      </c>
-      <c r="C169" s="8" t="s">
-        <v>1681</v>
       </c>
       <c r="D169" s="8" t="s">
         <v>897</v>
@@ -21320,21 +21302,21 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="8" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D170" s="8" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="13" t="s">
-        <v>1683</v>
+      <c r="A172" s="12" t="s">
+        <v>1682</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>34</v>
@@ -21342,13 +21324,13 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B173" s="3" t="s">
         <v>1388</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="C173" s="3" t="s">
         <v>1389</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>1390</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>6</v>
@@ -21356,13 +21338,13 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="8" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B174" s="8" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C174" s="8" t="s">
         <v>1684</v>
-      </c>
-      <c r="C174" s="8" t="s">
-        <v>1685</v>
       </c>
       <c r="D174" s="8" t="s">
         <v>867</v>
@@ -21370,13 +21352,13 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="8" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="D175" s="8" t="s">
         <v>940</v>
@@ -21384,27 +21366,27 @@
     </row>
     <row r="176" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="8" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="B176" s="8" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C176" s="8" t="s">
         <v>1687</v>
       </c>
-      <c r="C176" s="8" t="s">
+      <c r="D176" s="8" t="s">
         <v>1688</v>
-      </c>
-      <c r="D176" s="8" t="s">
-        <v>1689</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="8" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="B177" s="8" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C177" s="8" t="s">
         <v>1690</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>1691</v>
       </c>
       <c r="D177" s="8" t="s">
         <v>887</v>
@@ -21412,21 +21394,21 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="8" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="B178" s="8" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C178" s="8" t="s">
         <v>1692</v>
-      </c>
-      <c r="C178" s="8" t="s">
-        <v>1693</v>
       </c>
       <c r="D178" s="8" t="s">
         <v>897</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="13" t="s">
-        <v>1694</v>
+      <c r="A180" s="12" t="s">
+        <v>1693</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>29</v>
@@ -21434,16 +21416,16 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B181" s="3" t="s">
         <v>1695</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="C181" s="3" t="s">
         <v>1696</v>
       </c>
-      <c r="C181" s="3" t="s">
+      <c r="D181" s="3" t="s">
         <v>1697</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>1698</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>6</v>
@@ -21451,16 +21433,16 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="8" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B182" s="8" t="s">
         <v>1699</v>
       </c>
-      <c r="B182" s="8" t="s">
+      <c r="C182" s="8" t="s">
         <v>1700</v>
       </c>
-      <c r="C182" s="8" t="s">
+      <c r="D182" s="8" t="s">
         <v>1701</v>
-      </c>
-      <c r="D182" s="8" t="s">
-        <v>1702</v>
       </c>
       <c r="E182" s="8" t="s">
         <v>836</v>
@@ -21468,16 +21450,16 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="8" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B183" s="8" t="s">
         <v>1703</v>
       </c>
-      <c r="B183" s="8" t="s">
+      <c r="C183" s="8" t="s">
         <v>1704</v>
       </c>
-      <c r="C183" s="8" t="s">
+      <c r="D183" s="8" t="s">
         <v>1705</v>
-      </c>
-      <c r="D183" s="8" t="s">
-        <v>1706</v>
       </c>
       <c r="E183" s="8" t="s">
         <v>840</v>
@@ -21485,16 +21467,16 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="8" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B184" s="8" t="s">
         <v>1707</v>
       </c>
-      <c r="B184" s="8" t="s">
+      <c r="C184" s="8" t="s">
         <v>1708</v>
       </c>
-      <c r="C184" s="8" t="s">
+      <c r="D184" s="8" t="s">
         <v>1709</v>
-      </c>
-      <c r="D184" s="8" t="s">
-        <v>1710</v>
       </c>
       <c r="E184" s="8" t="s">
         <v>940</v>
@@ -21502,24 +21484,24 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="8" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B185" s="8" t="s">
         <v>1711</v>
       </c>
-      <c r="B185" s="8" t="s">
+      <c r="C185" s="8" t="s">
         <v>1712</v>
       </c>
-      <c r="C185" s="8" t="s">
+      <c r="D185" s="8" t="s">
         <v>1713</v>
-      </c>
-      <c r="D185" s="8" t="s">
-        <v>1714</v>
       </c>
       <c r="E185" s="8" t="s">
         <v>922</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="13" t="s">
-        <v>1715</v>
+      <c r="A187" s="12" t="s">
+        <v>1714</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>29</v>
@@ -21527,21 +21509,21 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="8" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="C189" s="8" t="s">
         <v>955</v>
@@ -21549,10 +21531,10 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="8" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C190" s="8" t="s">
         <v>961</v>
@@ -21560,10 +21542,10 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="8" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>965</v>
@@ -21571,18 +21553,18 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="8" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B192" s="8" t="s">
         <v>1719</v>
-      </c>
-      <c r="B192" s="8" t="s">
-        <v>1720</v>
       </c>
       <c r="C192" s="8" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="13" t="s">
-        <v>1721</v>
+      <c r="A194" s="12" t="s">
+        <v>1720</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>30</v>
@@ -21590,27 +21572,27 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="8" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D196" s="8" t="s">
         <v>983</v>
@@ -21618,13 +21600,13 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="8" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B197" s="8" t="s">
         <v>1558</v>
       </c>
-      <c r="B197" s="8" t="s">
-        <v>1559</v>
-      </c>
       <c r="C197" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>983</v>
@@ -21632,21 +21614,21 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="8" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C198" s="8" t="s">
         <v>1558</v>
       </c>
-      <c r="B198" s="8" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C198" s="8" t="s">
-        <v>1559</v>
-      </c>
       <c r="D198" s="8" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="12" t="s">
         <v>1724</v>
-      </c>
-    </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="13" t="s">
-        <v>1725</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>30</v>
@@ -21654,27 +21636,27 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B201" s="3" t="s">
         <v>1726</v>
       </c>
-      <c r="B201" s="3" t="s">
-        <v>1727</v>
-      </c>
       <c r="C201" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="D202" s="8" t="s">
         <v>1023</v>
@@ -21682,35 +21664,35 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="8" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B203" s="8" t="s">
         <v>1558</v>
       </c>
-      <c r="B203" s="8" t="s">
-        <v>1559</v>
-      </c>
       <c r="C203" s="8" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D203" s="8" t="s">
         <v>1728</v>
-      </c>
-      <c r="D203" s="8" t="s">
-        <v>1729</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="8" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C204" s="8" t="s">
         <v>1730</v>
-      </c>
-      <c r="B204" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="C204" s="8" t="s">
-        <v>1731</v>
       </c>
       <c r="D204" s="8" t="s">
         <v>1043</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="13" t="s">
-        <v>1732</v>
+      <c r="A206" s="12" t="s">
+        <v>1731</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>34</v>
@@ -21718,27 +21700,27 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B207" s="3" t="s">
         <v>1388</v>
       </c>
-      <c r="B207" s="3" t="s">
+      <c r="C207" s="3" t="s">
         <v>1389</v>
       </c>
-      <c r="C207" s="3" t="s">
-        <v>1390</v>
-      </c>
       <c r="D207" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="8" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B208" s="8" t="s">
         <v>1733</v>
       </c>
-      <c r="B208" s="8" t="s">
-        <v>1734</v>
-      </c>
       <c r="C208" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D208" s="8" t="s">
         <v>1116</v>
@@ -21746,13 +21728,13 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B209" s="8" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C209" s="8" t="s">
         <v>1735</v>
-      </c>
-      <c r="C209" s="8" t="s">
-        <v>1736</v>
       </c>
       <c r="D209" s="8" t="s">
         <v>1116</v>
@@ -21760,13 +21742,13 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="8" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B210" s="8" t="s">
         <v>1736</v>
       </c>
-      <c r="B210" s="8" t="s">
+      <c r="C210" s="8" t="s">
         <v>1737</v>
-      </c>
-      <c r="C210" s="8" t="s">
-        <v>1738</v>
       </c>
       <c r="D210" s="8" t="s">
         <v>1116</v>
@@ -21774,13 +21756,13 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="8" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="B211" s="8" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C211" s="8" t="s">
         <v>1739</v>
-      </c>
-      <c r="C211" s="8" t="s">
-        <v>1740</v>
       </c>
       <c r="D211" s="8" t="s">
         <v>1116</v>
@@ -21788,21 +21770,21 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="8" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B212" s="8" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C212" s="8" t="s">
         <v>1741</v>
-      </c>
-      <c r="C212" s="8" t="s">
-        <v>1742</v>
       </c>
       <c r="D212" s="8" t="s">
         <v>1121</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="13" t="s">
-        <v>1743</v>
+      <c r="A214" s="12" t="s">
+        <v>1742</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>29</v>
@@ -21810,21 +21792,21 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="8" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B216" s="8" t="s">
         <v>1745</v>
-      </c>
-      <c r="B216" s="8" t="s">
-        <v>1746</v>
       </c>
       <c r="C216" s="8" t="s">
         <v>1110</v>
@@ -21832,10 +21814,10 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="8" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B217" s="8" t="s">
         <v>1747</v>
-      </c>
-      <c r="B217" s="8" t="s">
-        <v>1748</v>
       </c>
       <c r="C217" s="8" t="s">
         <v>1082</v>
@@ -21843,10 +21825,10 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="8" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B218" s="8" t="s">
         <v>1749</v>
-      </c>
-      <c r="B218" s="8" t="s">
-        <v>1750</v>
       </c>
       <c r="C218" s="8" t="s">
         <v>1038</v>
@@ -21854,18 +21836,18 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="8" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B219" s="8" t="s">
         <v>1751</v>
-      </c>
-      <c r="B219" s="8" t="s">
-        <v>1752</v>
       </c>
       <c r="C219" s="8" t="s">
         <v>1126</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="13" t="s">
-        <v>1753</v>
+      <c r="A221" s="12" t="s">
+        <v>1752</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>32</v>
@@ -21873,21 +21855,21 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="8" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B223" s="8" t="s">
         <v>1755</v>
-      </c>
-      <c r="B223" s="8" t="s">
-        <v>1756</v>
       </c>
       <c r="C223" s="8" t="s">
         <v>1209</v>
@@ -21895,43 +21877,43 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="8" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B224" s="8" t="s">
         <v>1757</v>
       </c>
-      <c r="B224" s="8" t="s">
-        <v>1758</v>
-      </c>
       <c r="C224" s="8" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B225" s="8" t="s">
         <v>1759</v>
       </c>
-      <c r="B225" s="8" t="s">
-        <v>1760</v>
-      </c>
       <c r="C225" s="8" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="8" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="8" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B227" s="8" t="s">
         <v>1762</v>
-      </c>
-      <c r="B227" s="8" t="s">
-        <v>1763</v>
       </c>
       <c r="C227" s="8" t="s">
         <v>480</v>
@@ -21939,10 +21921,10 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="8" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C228" s="8" t="s">
         <v>484</v>
@@ -21950,10 +21932,10 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="8" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B229" s="8" t="s">
         <v>1765</v>
-      </c>
-      <c r="B229" s="8" t="s">
-        <v>1766</v>
       </c>
       <c r="C229" s="8" t="s">
         <v>494</v>
@@ -21961,10 +21943,10 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="8" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C230" s="8" t="s">
         <v>65</v>
